--- a/14_Options_Derivatives/_template_OPTIONS.xlsx
+++ b/14_Options_Derivatives/_template_OPTIONS.xlsx
@@ -352,80 +352,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -684,54 +688,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -754,136 +758,136 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <f aca="false">(LN(C5/C6)+(C8-C9+0.5*C10^2)*C7)/(C10*SQRT(C7))</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <f aca="false">F5-C10*SQRT(C7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <f aca="false">NORMSDIST(F5)</f>
         <v>0.559617692370243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <f aca="false">NORMSDIST(F6)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <f aca="false">NORMSDIST(-F5)</f>
         <v>0.440382307629758</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <f aca="false">NORMSDIST(-F6)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="13" t="n">
         <f aca="false">C5*EXP(-C9*C7)*F7-C6*EXP(-C8*C7)*F8</f>
         <v>6.5211170064626</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="13" t="n">
         <f aca="false">C6*EXP(-C8*C7)*F10-C5*EXP(-C9*C7)*F9</f>
         <v>5.4024214675859</v>
       </c>
@@ -907,109 +911,109 @@
   <dimension ref="A2:E9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="9" t="n">
         <f aca="false">EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*'BS Pricer'!$F$7</f>
         <v>0.559617692370243</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <f aca="false">-EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*'BS Pricer'!$F$9</f>
         <v>-0.440382307629758</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="9" t="n">
         <f aca="false">EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*(EXP(-('BS Pricer'!$F$5)^2/2)/SQRT(2*PI()))/('BS Pricer'!$C$5*'BS Pricer'!$C$10*SQRT('BS Pricer'!$C$7))</f>
         <v>0.026897048103991</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <f aca="false">EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*(EXP(-('BS Pricer'!$F$5)^2/2)/SQRT(2*PI()))/('BS Pricer'!$C$5*'BS Pricer'!$C$10*SQRT('BS Pricer'!$C$7))</f>
         <v>0.026897048103991</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <f aca="false">'BS Pricer'!$C$5*EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*(EXP(-('BS Pricer'!$F$5)^2/2)/SQRT(2*PI()))*SQRT('BS Pricer'!$C$7)/100</f>
         <v>0.201727860779933</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <f aca="false">'BS Pricer'!$C$5*EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*(EXP(-('BS Pricer'!$F$5)^2/2)/SQRT(2*PI()))*SQRT('BS Pricer'!$C$7)/100</f>
         <v>0.201727860779933</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <f aca="false">(-'BS Pricer'!$C$5*(EXP(-('BS Pricer'!$F$5)^2/2)/SQRT(2*PI()))*'BS Pricer'!$C$10*EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)/(2*SQRT('BS Pricer'!$C$7))-'BS Pricer'!$C$8*'BS Pricer'!$C$6*EXP(-'BS Pricer'!$C$8*'BS Pricer'!$C$7)*'BS Pricer'!$F$8+'BS Pricer'!$C$9*'BS Pricer'!$C$5*EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*'BS Pricer'!$F$7)/365</f>
         <v>-0.0392561671155377</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <f aca="false">(-'BS Pricer'!$C$5*(EXP(-('BS Pricer'!$F$5)^2/2)/SQRT(2*PI()))*'BS Pricer'!$C$10*EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)/(2*SQRT('BS Pricer'!$C$7))+'BS Pricer'!$C$8*'BS Pricer'!$C$6*EXP(-'BS Pricer'!$C$8*'BS Pricer'!$C$7)*'BS Pricer'!$F$10-'BS Pricer'!$C$9*'BS Pricer'!$C$5*EXP(-'BS Pricer'!$C$9*'BS Pricer'!$C$7)*'BS Pricer'!$F$9)/365</f>
         <v>-0.0270653213600567</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <f aca="false">'BS Pricer'!$C$6*'BS Pricer'!$C$7*EXP(-'BS Pricer'!$C$8*'BS Pricer'!$C$7)*'BS Pricer'!$F$8/100</f>
         <v>0.123601630576404</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <f aca="false">-'BS Pricer'!$C$6*'BS Pricer'!$C$7*EXP(-'BS Pricer'!$C$8*'BS Pricer'!$C$7)*'BS Pricer'!$F$10/100</f>
         <v>-0.123601630576404</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1032,219 +1036,219 @@
   <dimension ref="B2:K11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="16" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <f aca="false">MAX(C4-'BS Pricer'!$C$6,0)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <f aca="false">MAX(D4-'BS Pricer'!$C$6,0)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <f aca="false">MAX(E4-'BS Pricer'!$C$6,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <f aca="false">MAX(F4-'BS Pricer'!$C$6,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <f aca="false">MAX(G4-'BS Pricer'!$C$6,0)</f>
         <v>10</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="17" t="n">
         <f aca="false">MAX(H4-'BS Pricer'!$C$6,0)</f>
         <v>20</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="17" t="n">
         <f aca="false">MAX(I4-'BS Pricer'!$C$6,0)</f>
         <v>30</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-C4,0)</f>
         <v>30</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-D4,0)</f>
         <v>20</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-E4,0)</f>
         <v>10</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-F4,0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-G4,0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-H4,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="16" t="n">
+      <c r="I6" s="17" t="n">
         <f aca="false">MAX('BS Pricer'!$C$6-I4,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <f aca="false">C5+C6</f>
         <v>30</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">D5+D6</f>
         <v>20</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">E5+E6</f>
         <v>10</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <f aca="false">F5+F6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="17" t="n">
         <f aca="false">G5+G6</f>
         <v>10</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="17" t="n">
         <f aca="false">H5+H6</f>
         <v>20</v>
       </c>
-      <c r="I7" s="16" t="n">
+      <c r="I7" s="17" t="n">
         <f aca="false">I5+I6</f>
         <v>30</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="17" t="n">
         <f aca="false">'BS Pricer'!$C$13+'BS Pricer'!$C$14</f>
         <v>11.9235384740485</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <f aca="false">C7-C8</f>
         <v>18.0764615259515</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <f aca="false">D7-D8</f>
         <v>8.0764615259515</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">E7-E8</f>
         <v>-1.9235384740485</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">F7-F8</f>
         <v>-11.9235384740485</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <f aca="false">G7-G8</f>
         <v>-1.9235384740485</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <f aca="false">H7-H8</f>
         <v>8.0764615259515</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <f aca="false">I7-I8</f>
         <v>18.0764615259515</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1267,104 +1271,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/14_Options_Derivatives/_template_OPTIONS.xlsx
+++ b/14_Options_Derivatives/_template_OPTIONS.xlsx
@@ -1,129 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="European Pricer" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Implied Vol" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Greeks" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Vol Surface" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Portfolio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Scenario P&amp;L" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Checks" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Sources" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RefreshLog" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="European Pricer" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implied Vol" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Greeks" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vol Surface" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario P&amp;L" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
     <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
     <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00;[RED]&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00%;[RED]\(0.00%\);\-"/>
+    <numFmt numFmtId="166" formatCode="0.00%;[Red](0.00%);-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="170" formatCode="0.0%;[RED]\(0.0%\);\-"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
+    <numFmt numFmtId="170" formatCode="0.0%;[Red](0.0%);-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF111827"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -148,14 +117,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,22 +145,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="FF111827"/>
+        <color rgb="00111827"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thin">
@@ -201,365 +160,194 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="39">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111827"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -567,294 +355,404 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="36" customWidth="1" style="35" min="2" max="2"/>
-    <col width="46" customWidth="1" style="35" min="3" max="3"/>
-    <col width="12" customWidth="1" style="35" min="4" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[UNDERLYING] — Options &amp; Derivatives Model</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="38" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Underlying:</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>[Ticker / index / FX / commodity]</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="38" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Use case:</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Pricing / volatility / portfolio risk</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="38" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="38" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Next expiry / event:</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="38" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Refresh cadence:</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Daily near expiry; weekly otherwise</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="38" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Active scenario:</t>
         </is>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="38" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Units:</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Per option unless noted</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="36">
-      <c r="B13" s="40" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Modeling conventions</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="36">
-      <c r="B14" s="41" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Blue text / yellow fill</t>
         </is>
       </c>
-      <c r="C14" s="42" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Hardcoded input or selected scenario</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="36">
-      <c r="B15" s="38" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C15" s="42" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Formula / same-sheet calculation</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="36">
-      <c r="B16" s="43" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C16" s="42" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cross-sheet formula / link</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="36">
-      <c r="B17" s="38" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="C17" s="42" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>PASS / REVIEW / FAIL must remain visible</t>
         </is>
@@ -866,324 +764,328 @@
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Downside"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:M10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="22" customWidth="1" style="35" min="2" max="2"/>
-    <col width="12" customWidth="1" style="35" min="3" max="4"/>
-    <col width="13" customWidth="1" style="35" min="5" max="7"/>
-    <col width="14" customWidth="1" style="35" min="8" max="12"/>
-    <col width="16" customWidth="1" style="35" min="13" max="13"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Options Portfolio Greeks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Leg</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Strike</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Vol</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Vega</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Theta</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Market value</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="35" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Core call</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Call</t>
         </is>
       </c>
-      <c r="D5" s="66" t="n">
+      <c r="D5" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="66" t="n">
+      <c r="F5" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="54" t="n">
+      <c r="G5" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="H5" s="61">
+      <c r="H5" s="20">
         <f>IF($C5="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-E5*EXP(-Assumptions!$E$8*F5)*NORMSDIST(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-G5*SQRT(F5)),E5*EXP(-Assumptions!$E$8*F5)*NORMSDIST(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-G5*SQRT(F5)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*NORMSDIST(-((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))))</f>
         <v/>
       </c>
-      <c r="I5" s="35">
+      <c r="I5">
         <f>IF($C5="Call",EXP(-Assumptions!$E$9*F5)*NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5))),EXP(-Assumptions!$E$9*F5)*(NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-1))*D5</f>
         <v/>
       </c>
-      <c r="J5" s="35">
+      <c r="J5">
         <f>EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G5*SQRT(F5))*D5</f>
         <v/>
       </c>
-      <c r="K5" s="35">
+      <c r="K5">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))*SQRT(F5)*D5</f>
         <v/>
       </c>
-      <c r="L5" s="35">
+      <c r="L5">
         <f>-Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))*G5/(2*SQRT(F5))*D5</f>
         <v/>
       </c>
-      <c r="M5" s="67">
+      <c r="M5" s="26">
         <f>H5*D5*Assumptions!$E$12</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="35" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Protective put</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Put</t>
         </is>
       </c>
-      <c r="D6" s="66" t="n">
+      <c r="D6" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="50" t="n">
+      <c r="E6" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="F6" s="66" t="n">
+      <c r="F6" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="20">
         <f>IF($C6="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-E6*EXP(-Assumptions!$E$8*F6)*NORMSDIST(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-G6*SQRT(F6)),E6*EXP(-Assumptions!$E$8*F6)*NORMSDIST(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-G6*SQRT(F6)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*NORMSDIST(-((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))))</f>
         <v/>
       </c>
-      <c r="I6" s="35">
+      <c r="I6">
         <f>IF($C6="Call",EXP(-Assumptions!$E$9*F6)*NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6))),EXP(-Assumptions!$E$9*F6)*(NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-1))*D6</f>
         <v/>
       </c>
-      <c r="J6" s="35">
+      <c r="J6">
         <f>EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G6*SQRT(F6))*D6</f>
         <v/>
       </c>
-      <c r="K6" s="35">
+      <c r="K6">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))*SQRT(F6)*D6</f>
         <v/>
       </c>
-      <c r="L6" s="35">
+      <c r="L6">
         <f>-Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))*G6/(2*SQRT(F6))*D6</f>
         <v/>
       </c>
-      <c r="M6" s="67">
+      <c r="M6" s="26">
         <f>H6*D6*Assumptions!$E$12</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="35" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Short call</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Call</t>
         </is>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="25" t="n">
         <v>-5</v>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="F7" s="66" t="n">
+      <c r="F7" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="54" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.24</v>
       </c>
-      <c r="H7" s="61">
+      <c r="H7" s="20">
         <f>IF($C7="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-E7*EXP(-Assumptions!$E$8*F7)*NORMSDIST(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-G7*SQRT(F7)),E7*EXP(-Assumptions!$E$8*F7)*NORMSDIST(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-G7*SQRT(F7)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*NORMSDIST(-((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))))</f>
         <v/>
       </c>
-      <c r="I7" s="35">
+      <c r="I7">
         <f>IF($C7="Call",EXP(-Assumptions!$E$9*F7)*NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7))),EXP(-Assumptions!$E$9*F7)*(NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-1))*D7</f>
         <v/>
       </c>
-      <c r="J7" s="35">
+      <c r="J7">
         <f>EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G7*SQRT(F7))*D7</f>
         <v/>
       </c>
-      <c r="K7" s="35">
+      <c r="K7">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))*SQRT(F7)*D7</f>
         <v/>
       </c>
-      <c r="L7" s="35">
+      <c r="L7">
         <f>-Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))*G7/(2*SQRT(F7))*D7</f>
         <v/>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="26">
         <f>H7*D7*Assumptions!$E$12</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="35" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Long-dated call</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Call</t>
         </is>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="9" t="n">
         <v>105</v>
       </c>
-      <c r="F8" s="66" t="n">
+      <c r="F8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.27</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="20">
         <f>IF($C8="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-E8*EXP(-Assumptions!$E$8*F8)*NORMSDIST(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-G8*SQRT(F8)),E8*EXP(-Assumptions!$E$8*F8)*NORMSDIST(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-G8*SQRT(F8)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*NORMSDIST(-((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))))</f>
         <v/>
       </c>
-      <c r="I8" s="35">
+      <c r="I8">
         <f>IF($C8="Call",EXP(-Assumptions!$E$9*F8)*NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8))),EXP(-Assumptions!$E$9*F8)*(NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-1))*D8</f>
         <v/>
       </c>
-      <c r="J8" s="35">
+      <c r="J8">
         <f>EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G8*SQRT(F8))*D8</f>
         <v/>
       </c>
-      <c r="K8" s="35">
+      <c r="K8">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))*SQRT(F8)*D8</f>
         <v/>
       </c>
-      <c r="L8" s="35">
+      <c r="L8">
         <f>-Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))*G8/(2*SQRT(F8))*D8</f>
         <v/>
       </c>
-      <c r="M8" s="67">
+      <c r="M8" s="26">
         <f>H8*D8*Assumptions!$E$12</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="68" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Portfolio total</t>
         </is>
       </c>
-      <c r="C10" s="68" t="n"/>
-      <c r="D10" s="68" t="n"/>
-      <c r="E10" s="68" t="n"/>
-      <c r="F10" s="68" t="n"/>
-      <c r="G10" s="68" t="n"/>
-      <c r="H10" s="68" t="n"/>
-      <c r="I10" s="69">
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="28">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
-      <c r="J10" s="69">
+      <c r="J10" s="28">
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="K10" s="69">
+      <c r="K10" s="28">
         <f>SUM(K5:K8)</f>
         <v/>
       </c>
-      <c r="L10" s="69">
+      <c r="L10" s="28">
         <f>SUM(L5:L8)</f>
         <v/>
       </c>
-      <c r="M10" s="70">
+      <c r="M10" s="29">
         <f>SUM(M5:M8)</f>
         <v/>
       </c>
@@ -1192,176 +1094,178 @@
   <mergeCells count="1">
     <mergeCell ref="B2:M2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="24" customWidth="1" style="35" min="2" max="2"/>
-    <col width="14" customWidth="1" style="35" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Delta-Gamma-Vega Scenario P&amp;L</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Spot shock / Vol shock</t>
         </is>
       </c>
-      <c r="C4" s="71" t="n">
+      <c r="C4" s="30" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D4" s="71" t="n">
+      <c r="D4" s="30" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E4" s="71" t="n">
+      <c r="E4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="71" t="n">
+      <c r="F4" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="G4" s="71" t="n">
+      <c r="G4" s="30" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="72" t="n">
+    <row r="5">
+      <c r="B5" s="31" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*C$4</f>
         <v/>
       </c>
-      <c r="D5" s="67">
+      <c r="D5" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*D$4</f>
         <v/>
       </c>
-      <c r="E5" s="67">
+      <c r="E5" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*E$4</f>
         <v/>
       </c>
-      <c r="F5" s="67">
+      <c r="F5" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*F$4</f>
         <v/>
       </c>
-      <c r="G5" s="67">
+      <c r="G5" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*G$4</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="72" t="n">
+    <row r="6">
+      <c r="B6" s="31" t="n">
         <v>-0.1</v>
       </c>
-      <c r="C6" s="67">
+      <c r="C6" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*C$4</f>
         <v/>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*D$4</f>
         <v/>
       </c>
-      <c r="E6" s="67">
+      <c r="E6" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*E$4</f>
         <v/>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*F$4</f>
         <v/>
       </c>
-      <c r="G6" s="67">
+      <c r="G6" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*G$4</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="72" t="n">
+    <row r="7">
+      <c r="B7" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="67">
+      <c r="C7" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*C$4</f>
         <v/>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*D$4</f>
         <v/>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*E$4</f>
         <v/>
       </c>
-      <c r="F7" s="67">
+      <c r="F7" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*F$4</f>
         <v/>
       </c>
-      <c r="G7" s="67">
+      <c r="G7" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*G$4</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="72" t="n">
+    <row r="8">
+      <c r="B8" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*C$4</f>
         <v/>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*D$4</f>
         <v/>
       </c>
-      <c r="E8" s="67">
+      <c r="E8" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*E$4</f>
         <v/>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*F$4</f>
         <v/>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*G$4</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="72" t="n">
+    <row r="9">
+      <c r="B9" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="C9" s="67">
+      <c r="C9" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*C$4</f>
         <v/>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*D$4</f>
         <v/>
       </c>
-      <c r="E9" s="67">
+      <c r="E9" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*E$4</f>
         <v/>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*F$4</f>
         <v/>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="26">
         <f>Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*G$4</f>
         <v/>
       </c>
@@ -1371,118 +1275,116 @@
     <mergeCell ref="B2:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFFCE4D6"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFE2F0D9"/>
+        <cfvo type="max"/>
+        <color rgb="00FCE4D6"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00E2F0D9"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="42" customWidth="1" style="35" min="2" max="2"/>
-    <col width="18" customWidth="1" style="35" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Model Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="35" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Put-call parity</t>
         </is>
       </c>
-      <c r="C5" s="35">
+      <c r="C5">
         <f>IF(ABS('European Pricer'!C13)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="35" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Implied volatility convergence</t>
         </is>
       </c>
-      <c r="C6" s="35">
+      <c r="C6">
         <f>IF('Implied Vol'!E17&lt;0.0001,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="35" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Gamma positive</t>
         </is>
       </c>
-      <c r="C7" s="35">
+      <c r="C7">
         <f>IF(AND(Greeks!C6&gt;0,Greeks!D6&gt;0),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="35" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Call price within bounds</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8">
         <f>IF(AND('European Pricer'!C7&gt;=MAX(0,Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)),'European Pricer'!C7&lt;=Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="35" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Portfolio formulas populated</t>
         </is>
       </c>
-      <c r="C9" s="35">
+      <c r="C9">
         <f>IF(COUNT(Portfolio!H5:M8)=24,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="35" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10">
         <f>IF(COUNTIF(C5:C9,"FAIL")=0,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -1492,153 +1394,151 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C10">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="34" customWidth="1" style="35" min="2" max="2"/>
-    <col width="58" customWidth="1" style="35" min="3" max="3"/>
-    <col width="16" customWidth="1" style="35" min="4" max="4"/>
-    <col width="48" customWidth="1" style="35" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Source Register</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Input / dataset</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Source URL or document</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes / transformation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="73" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Option contract specification</t>
         </is>
       </c>
-      <c r="C5" s="73" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>[exchange / broker URL]</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E5" s="73" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Multiplier, expiry, settlement, exercise style</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="73" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Underlying and option market data</t>
         </is>
       </c>
-      <c r="C6" s="73" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>[market data URL]</t>
         </is>
       </c>
-      <c r="D6" s="73" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
-      <c r="E6" s="73" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>Spot, bid/ask, implied volatility</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="73" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Risk-free curve</t>
         </is>
       </c>
-      <c r="C7" s="73" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>https://home.treasury.gov/resource-center/data-chart-center/interest-rates</t>
         </is>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E7" s="73" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Document interpolation and currency basis</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="73" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Dividend / carry assumption</t>
         </is>
       </c>
-      <c r="C8" s="73" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>[issuer or market source]</t>
         </is>
       </c>
-      <c r="D8" s="73" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E8" s="73" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Expected dividends or foreign rates</t>
         </is>
@@ -1648,276 +1548,272 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="14" customWidth="1" style="35" min="2" max="2"/>
-    <col width="22" customWidth="1" style="35" min="3" max="3"/>
-    <col width="28" customWidth="1" style="35" min="4" max="4"/>
-    <col width="38" customWidth="1" style="35" min="5" max="5"/>
-    <col width="34" customWidth="1" style="35" min="6" max="6"/>
-    <col width="18" customWidth="1" style="35" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Source snapshot</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Reviewer / challenge</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="74" t="n"/>
-      <c r="C5" s="74" t="n"/>
-      <c r="D5" s="74" t="n"/>
-      <c r="E5" s="74" t="n"/>
-      <c r="F5" s="74" t="n"/>
-      <c r="G5" s="74" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="74" t="n"/>
-      <c r="C6" s="74" t="n"/>
-      <c r="D6" s="74" t="n"/>
-      <c r="E6" s="74" t="n"/>
-      <c r="F6" s="74" t="n"/>
-      <c r="G6" s="74" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="74" t="n"/>
-      <c r="C7" s="74" t="n"/>
-      <c r="D7" s="74" t="n"/>
-      <c r="E7" s="74" t="n"/>
-      <c r="F7" s="74" t="n"/>
-      <c r="G7" s="74" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="74" t="n"/>
-      <c r="C8" s="74" t="n"/>
-      <c r="D8" s="74" t="n"/>
-      <c r="E8" s="74" t="n"/>
-      <c r="F8" s="74" t="n"/>
-      <c r="G8" s="74" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="74" t="n"/>
-      <c r="C9" s="74" t="n"/>
-      <c r="D9" s="74" t="n"/>
-      <c r="E9" s="74" t="n"/>
-      <c r="F9" s="74" t="n"/>
-      <c r="G9" s="74" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="74" t="n"/>
-      <c r="C10" s="74" t="n"/>
-      <c r="D10" s="74" t="n"/>
-      <c r="E10" s="74" t="n"/>
-      <c r="F10" s="74" t="n"/>
-      <c r="G10" s="74" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="36">
-      <c r="B11" s="74" t="n"/>
-      <c r="C11" s="74" t="n"/>
-      <c r="D11" s="74" t="n"/>
-      <c r="E11" s="74" t="n"/>
-      <c r="F11" s="74" t="n"/>
-      <c r="G11" s="74" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="36">
-      <c r="B12" s="74" t="n"/>
-      <c r="C12" s="74" t="n"/>
-      <c r="D12" s="74" t="n"/>
-      <c r="E12" s="74" t="n"/>
-      <c r="F12" s="74" t="n"/>
-      <c r="G12" s="74" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="36">
-      <c r="B13" s="74" t="n"/>
-      <c r="C13" s="74" t="n"/>
-      <c r="D13" s="74" t="n"/>
-      <c r="E13" s="74" t="n"/>
-      <c r="F13" s="74" t="n"/>
-      <c r="G13" s="74" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="36">
-      <c r="B14" s="74" t="n"/>
-      <c r="C14" s="74" t="n"/>
-      <c r="D14" s="74" t="n"/>
-      <c r="E14" s="74" t="n"/>
-      <c r="F14" s="74" t="n"/>
-      <c r="G14" s="74" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="36">
-      <c r="B15" s="74" t="n"/>
-      <c r="C15" s="74" t="n"/>
-      <c r="D15" s="74" t="n"/>
-      <c r="E15" s="74" t="n"/>
-      <c r="F15" s="74" t="n"/>
-      <c r="G15" s="74" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="36">
-      <c r="B16" s="74" t="n"/>
-      <c r="C16" s="74" t="n"/>
-      <c r="D16" s="74" t="n"/>
-      <c r="E16" s="74" t="n"/>
-      <c r="F16" s="74" t="n"/>
-      <c r="G16" s="74" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="36">
-      <c r="B17" s="74" t="n"/>
-      <c r="C17" s="74" t="n"/>
-      <c r="D17" s="74" t="n"/>
-      <c r="E17" s="74" t="n"/>
-      <c r="F17" s="74" t="n"/>
-      <c r="G17" s="74" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="36">
-      <c r="B18" s="74" t="n"/>
-      <c r="C18" s="74" t="n"/>
-      <c r="D18" s="74" t="n"/>
-      <c r="E18" s="74" t="n"/>
-      <c r="F18" s="74" t="n"/>
-      <c r="G18" s="74" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="36">
-      <c r="B19" s="74" t="n"/>
-      <c r="C19" s="74" t="n"/>
-      <c r="D19" s="74" t="n"/>
-      <c r="E19" s="74" t="n"/>
-      <c r="F19" s="74" t="n"/>
-      <c r="G19" s="74" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="36">
-      <c r="B20" s="74" t="n"/>
-      <c r="C20" s="74" t="n"/>
-      <c r="D20" s="74" t="n"/>
-      <c r="E20" s="74" t="n"/>
-      <c r="F20" s="74" t="n"/>
-      <c r="G20" s="74" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="36">
-      <c r="B21" s="74" t="n"/>
-      <c r="C21" s="74" t="n"/>
-      <c r="D21" s="74" t="n"/>
-      <c r="E21" s="74" t="n"/>
-      <c r="F21" s="74" t="n"/>
-      <c r="G21" s="74" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="36">
-      <c r="B22" s="74" t="n"/>
-      <c r="C22" s="74" t="n"/>
-      <c r="D22" s="74" t="n"/>
-      <c r="E22" s="74" t="n"/>
-      <c r="F22" s="74" t="n"/>
-      <c r="G22" s="74" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="36">
-      <c r="B23" s="74" t="n"/>
-      <c r="C23" s="74" t="n"/>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="74" t="n"/>
-      <c r="F23" s="74" t="n"/>
-      <c r="G23" s="74" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="36">
-      <c r="B24" s="74" t="n"/>
-      <c r="C24" s="74" t="n"/>
-      <c r="D24" s="74" t="n"/>
-      <c r="E24" s="74" t="n"/>
-      <c r="F24" s="74" t="n"/>
-      <c r="G24" s="74" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="36">
-      <c r="B25" s="74" t="n"/>
-      <c r="C25" s="74" t="n"/>
-      <c r="D25" s="74" t="n"/>
-      <c r="E25" s="74" t="n"/>
-      <c r="F25" s="74" t="n"/>
-      <c r="G25" s="74" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="36">
-      <c r="B26" s="74" t="n"/>
-      <c r="C26" s="74" t="n"/>
-      <c r="D26" s="74" t="n"/>
-      <c r="E26" s="74" t="n"/>
-      <c r="F26" s="74" t="n"/>
-      <c r="G26" s="74" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="36">
-      <c r="B27" s="74" t="n"/>
-      <c r="C27" s="74" t="n"/>
-      <c r="D27" s="74" t="n"/>
-      <c r="E27" s="74" t="n"/>
-      <c r="F27" s="74" t="n"/>
-      <c r="G27" s="74" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="36">
-      <c r="B28" s="74" t="n"/>
-      <c r="C28" s="74" t="n"/>
-      <c r="D28" s="74" t="n"/>
-      <c r="E28" s="74" t="n"/>
-      <c r="F28" s="74" t="n"/>
-      <c r="G28" s="74" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="36">
-      <c r="B29" s="74" t="n"/>
-      <c r="C29" s="74" t="n"/>
-      <c r="D29" s="74" t="n"/>
-      <c r="E29" s="74" t="n"/>
-      <c r="F29" s="74" t="n"/>
-      <c r="G29" s="74" t="n"/>
+    <row r="5">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="33" t="n"/>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="33" t="n"/>
+      <c r="G7" s="33" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="33" t="n"/>
+      <c r="C9" s="33" t="n"/>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n"/>
+      <c r="F9" s="33" t="n"/>
+      <c r="G9" s="33" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="33" t="n"/>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="33" t="n"/>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="33" t="n"/>
+      <c r="G11" s="33" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="33" t="n"/>
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="33" t="n"/>
+      <c r="G12" s="33" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="33" t="n"/>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n"/>
+      <c r="F13" s="33" t="n"/>
+      <c r="G13" s="33" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="33" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="33" t="n"/>
+      <c r="F15" s="33" t="n"/>
+      <c r="G15" s="33" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="33" t="n"/>
+      <c r="F16" s="33" t="n"/>
+      <c r="G16" s="33" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="33" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="33" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="33" t="n"/>
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="33" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="33" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="33" t="n"/>
+      <c r="C19" s="33" t="n"/>
+      <c r="D19" s="33" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="33" t="n"/>
+      <c r="G19" s="33" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="33" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="33" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="33" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="33" t="n"/>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="33" t="n"/>
+      <c r="E23" s="33" t="n"/>
+      <c r="F23" s="33" t="n"/>
+      <c r="G23" s="33" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="33" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="33" t="n"/>
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="33" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="33" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="33" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="33" t="n"/>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="33" t="n"/>
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="33" t="n"/>
+      <c r="E29" s="33" t="n"/>
+      <c r="F29" s="33" t="n"/>
+      <c r="G29" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1930,133 +1826,133 @@
   <dimension ref="B2:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="36" min="2" max="2"/>
-    <col width="48" customWidth="1" style="36" min="3" max="3"/>
-    <col width="24" customWidth="1" style="36" min="4" max="4"/>
-    <col width="34" customWidth="1" style="36" min="5" max="5"/>
-    <col width="20" customWidth="1" style="36" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Options &amp; Derivatives — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Options &amp; Derivatives</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>tools/builders/build_options_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>trading desk, market making, independent risk and model validation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>volatility and Greeks risk pack</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>intraday desk; daily risk and margin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="47" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="48" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="48" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="48" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="48" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2148,34 +2044,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="48" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="48" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="48" t="inlineStr">
+      <c r="F21" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2267,34 +2163,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="47" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="48" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="48" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="48" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="48" t="inlineStr">
+      <c r="E29" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="48" t="inlineStr">
+      <c r="F29" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2386,34 +2282,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="47" t="inlineStr">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="48" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="48" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="48" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="48" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="48" t="inlineStr">
+      <c r="F37" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2505,34 +2401,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="47" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="48" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="48" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="48" t="inlineStr">
+      <c r="D45" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="48" t="inlineStr">
+      <c r="E45" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="48" t="inlineStr">
+      <c r="F45" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2624,34 +2520,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="47" t="inlineStr">
+      <c r="B52" s="37" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="48" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="48" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="48" t="inlineStr">
+      <c r="D53" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="48" t="inlineStr">
+      <c r="E53" s="38" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="48" t="inlineStr">
+      <c r="F53" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2743,34 +2639,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="47" t="inlineStr">
+      <c r="B60" s="37" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="48" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="48" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="48" t="inlineStr">
+      <c r="D61" s="38" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="48" t="inlineStr">
+      <c r="E61" s="38" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="48" t="inlineStr">
+      <c r="F61" s="38" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -2896,60 +2792,60 @@
   <dimension ref="B2:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="36" min="2" max="2"/>
-    <col width="22" customWidth="1" style="36" min="3" max="3"/>
-    <col width="52" customWidth="1" style="36" min="4" max="4"/>
-    <col width="46" customWidth="1" style="36" min="5" max="5"/>
-    <col width="36" customWidth="1" style="36" min="6" max="6"/>
-    <col width="14" customWidth="1" style="36" min="7" max="7"/>
-    <col width="18" customWidth="1" style="36" min="8" max="8"/>
-    <col width="14" customWidth="1" style="36" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="38" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="38" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3070,66 +2966,66 @@
   <dimension ref="B2:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="36" min="2" max="2"/>
-    <col width="18" customWidth="1" style="36" min="3" max="3"/>
-    <col width="42" customWidth="1" style="36" min="4" max="4"/>
-    <col width="24" customWidth="1" style="36" min="5" max="5"/>
-    <col width="18" customWidth="1" style="36" min="6" max="6"/>
-    <col width="22" customWidth="1" style="36" min="7" max="7"/>
-    <col width="42" customWidth="1" style="36" min="8" max="8"/>
-    <col width="30" customWidth="1" style="36" min="9" max="9"/>
-    <col width="15" customWidth="1" style="36" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="38" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="38" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="38" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3258,290 +3154,292 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="34" customWidth="1" style="35" min="2" max="2"/>
-    <col width="15" customWidth="1" style="35" min="3" max="5"/>
-    <col width="30" customWidth="1" style="35" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Pricing and Risk Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Units / note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="35" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Spot price</t>
         </is>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="C5" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="10">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="35" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Strike price</t>
         </is>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="10">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="35" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Time to expiry</t>
         </is>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="12">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="35" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Risk-free rate</t>
         </is>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="D8" s="54" t="n">
+      <c r="D8" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="14">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="35" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Dividend yield</t>
         </is>
       </c>
-      <c r="C9" s="54" t="n">
+      <c r="C9" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="14">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="35" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Implied volatility</t>
         </is>
       </c>
-      <c r="C10" s="54" t="n">
+      <c r="C10" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="54" t="n">
+      <c r="D10" s="13" t="n">
         <v>0.45</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="14">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="35" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="36">
-      <c r="B11" s="35" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Observed call price</t>
         </is>
       </c>
-      <c r="C11" s="50" t="n">
+      <c r="C11" s="9" t="n">
         <v>8.25</v>
       </c>
-      <c r="D11" s="50" t="n">
+      <c r="D11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="10">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="36">
-      <c r="B12" s="35" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Contract multiplier</t>
         </is>
       </c>
-      <c r="C12" s="56" t="n">
+      <c r="C12" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="D12" s="56" t="n">
+      <c r="D12" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="16">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="36">
-      <c r="B13" s="35" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Position count</t>
         </is>
       </c>
-      <c r="C13" s="56" t="n">
+      <c r="C13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="56" t="n">
+      <c r="D13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="16">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>contracts</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="36">
-      <c r="B14" s="35" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Strike skew slope</t>
         </is>
       </c>
-      <c r="C14" s="58" t="n">
+      <c r="C14" s="17" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D14" s="58" t="n">
+      <c r="D14" s="17" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E14" s="59">
+      <c r="E14" s="18">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>vol per moneyness</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="36">
-      <c r="B15" s="35" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Term-vol slope</t>
         </is>
       </c>
-      <c r="C15" s="58" t="n">
+      <c r="C15" s="17" t="n">
         <v>0.02</v>
       </c>
-      <c r="D15" s="58" t="n">
+      <c r="D15" s="17" t="n">
         <v>0.04</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="18">
         <f>IF(Cover!$C$9="Downside",D15,C15)</f>
         <v/>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>vol per log-year</t>
         </is>
@@ -3551,252 +3449,250 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="30" customWidth="1" style="35" min="2" max="2"/>
-    <col width="18" customWidth="1" style="35" min="3" max="3"/>
-    <col width="14" customWidth="1" style="35" min="4" max="4"/>
-    <col width="36" customWidth="1" style="35" min="5" max="5"/>
-    <col width="14" customWidth="1" style="35" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>European Black-Scholes Pricer</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Formula role</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="35" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>d1</t>
         </is>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="19">
         <f>(LN(Assumptions!E5/Assumptions!E6)+(Assumptions!E8-Assumptions!E9+0.5*Assumptions!E10^2)*Assumptions!E7)/(Assumptions!E10*SQRT(Assumptions!E7))</f>
         <v/>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>standardized moneyness</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="35" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>d2</t>
         </is>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="19">
         <f>C5-Assumptions!E10*SQRT(Assumptions!E7)</f>
         <v/>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>d1 less volatility-time</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="35" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Call price</t>
         </is>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="10">
         <f>Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)*NORMSDIST(C5)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)*NORMSDIST(C6)</f>
         <v/>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>discounted expected payoff</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="35" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Put price</t>
         </is>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="10">
         <f>Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)*NORMSDIST(-C6)-Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)*NORMSDIST(-C5)</f>
         <v/>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>discounted expected payoff</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="35" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Call intrinsic value</t>
         </is>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="10">
         <f>MAX(0,Assumptions!E5-Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>spot intrinsic</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="35" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Put intrinsic value</t>
         </is>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="10">
         <f>MAX(0,Assumptions!E6-Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>spot intrinsic</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="36">
-      <c r="B11" s="35" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Call time value</t>
         </is>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="10">
         <f>C7-C9</f>
         <v/>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>price less intrinsic</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="36">
-      <c r="B12" s="35" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Put time value</t>
         </is>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="10">
         <f>C8-C10</f>
         <v/>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>price less intrinsic</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="36">
-      <c r="B13" s="35" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Put-call parity residual</t>
         </is>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="19">
         <f>C7-C8-(Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7))</f>
         <v/>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>must equal zero</t>
         </is>
       </c>
-      <c r="F13" s="35">
+      <c r="F13">
         <f>IF(ABS(C13)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -3806,342 +3702,345 @@
     <mergeCell ref="B2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="F13">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>F13="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>F13="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>F13="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>F13="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="16" customWidth="1" style="35" min="2" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Newton-Raphson Implied Volatility</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Iteration</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Model call</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Observed call</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Price error</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Vega</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="35" t="n">
+    <row r="5">
+      <c r="B5" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="54" t="n">
+      <c r="C5" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C5^2)*Assumptions!$E$7)/(C5*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C5^2)*Assumptions!$E$7)/(C5*SQRT(Assumptions!$E$7)))-C5*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="20">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C5^2)*Assumptions!$E$7)/(C5*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="35" t="n">
+    <row r="6">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="22">
         <f>MAX(0.0001,C5-F5/MAX(0.000001,G5))</f>
         <v/>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C6^2)*Assumptions!$E$7)/(C6*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C6^2)*Assumptions!$E$7)/(C6*SQRT(Assumptions!$E$7)))-C6*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="20">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C6^2)*Assumptions!$E$7)/(C6*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="35" t="n">
+    <row r="7">
+      <c r="B7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="22">
         <f>MAX(0.0001,C6-F6/MAX(0.000001,G6))</f>
         <v/>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C7^2)*Assumptions!$E$7)/(C7*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C7^2)*Assumptions!$E$7)/(C7*SQRT(Assumptions!$E$7)))-C7*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="20">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C7^2)*Assumptions!$E$7)/(C7*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="35" t="n">
+    <row r="8">
+      <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="22">
         <f>MAX(0.0001,C7-F7/MAX(0.000001,G7))</f>
         <v/>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C8^2)*Assumptions!$E$7)/(C8*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C8^2)*Assumptions!$E$7)/(C8*SQRT(Assumptions!$E$7)))-C8*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="20">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C8^2)*Assumptions!$E$7)/(C8*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="35" t="n">
+    <row r="9">
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="22">
         <f>MAX(0.0001,C8-F8/MAX(0.000001,G8))</f>
         <v/>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C9^2)*Assumptions!$E$7)/(C9*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C9^2)*Assumptions!$E$7)/(C9*SQRT(Assumptions!$E$7)))-C9*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="20">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C9^2)*Assumptions!$E$7)/(C9*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="36">
-      <c r="B10" s="35" t="n">
+    <row r="10">
+      <c r="B10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="22">
         <f>MAX(0.0001,C9-F9/MAX(0.000001,G9))</f>
         <v/>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C10^2)*Assumptions!$E$7)/(C10*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C10^2)*Assumptions!$E$7)/(C10*SQRT(Assumptions!$E$7)))-C10*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="20">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C10^2)*Assumptions!$E$7)/(C10*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="36">
-      <c r="B11" s="35" t="n">
+    <row r="11">
+      <c r="B11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="22">
         <f>MAX(0.0001,C10-F10/MAX(0.000001,G10))</f>
         <v/>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C11^2)*Assumptions!$E$7)/(C11*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C11^2)*Assumptions!$E$7)/(C11*SQRT(Assumptions!$E$7)))-C11*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="20">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C11^2)*Assumptions!$E$7)/(C11*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="36">
-      <c r="B12" s="35" t="n">
+    <row r="12">
+      <c r="B12" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="63">
+      <c r="C12" s="22">
         <f>MAX(0.0001,C11-F11/MAX(0.000001,G11))</f>
         <v/>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C12^2)*Assumptions!$E$7)/(C12*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C12^2)*Assumptions!$E$7)/(C12*SQRT(Assumptions!$E$7)))-C12*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="20">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C12^2)*Assumptions!$E$7)/(C12*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="36">
-      <c r="B13" s="35" t="n">
+    <row r="13">
+      <c r="B13" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="22">
         <f>MAX(0.0001,C12-F12/MAX(0.000001,G12))</f>
         <v/>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C13^2)*Assumptions!$E$7)/(C13*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C13^2)*Assumptions!$E$7)/(C13*SQRT(Assumptions!$E$7)))-C13*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="20">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C13^2)*Assumptions!$E$7)/(C13*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="36">
-      <c r="B14" s="35" t="n">
+    <row r="14">
+      <c r="B14" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="22">
         <f>MAX(0.0001,C13-F13/MAX(0.000001,G13))</f>
         <v/>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="20">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C14^2)*Assumptions!$E$7)/(C14*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C14^2)*Assumptions!$E$7)/(C14*SQRT(Assumptions!$E$7)))-C14*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="10">
         <f>Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="20">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="62">
+      <c r="G14" s="21">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C14^2)*Assumptions!$E$7)/(C14*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="36">
-      <c r="B17" s="35" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Converged implied volatility</t>
         </is>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="22">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Final absolute price error</t>
         </is>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="20">
         <f>ABS(F14)</f>
         <v/>
       </c>
@@ -4150,151 +4049,150 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="22" customWidth="1" style="35" min="2" max="2"/>
-    <col width="18" customWidth="1" style="35" min="3" max="4"/>
-    <col width="40" customWidth="1" style="35" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>European Greeks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Greek</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Call</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Put</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="35" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="C5" s="64">
+      <c r="C5" s="23">
         <f>EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$5)</f>
         <v/>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="23">
         <f>EXP(-Assumptions!$E$9*Assumptions!$E$7)*(NORMSDIST('European Pricer'!$C$5)-1)</f>
         <v/>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>first-order spot exposure</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="35" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Gamma</t>
         </is>
       </c>
-      <c r="C6" s="64">
+      <c r="C6" s="23">
         <f>EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*Assumptions!$E$10*SQRT(Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="23">
         <f>C6</f>
         <v/>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>delta curvature</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="35" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Vega</t>
         </is>
       </c>
-      <c r="C7" s="64">
+      <c r="C7" s="23">
         <f>Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="D7" s="64">
+      <c r="D7" s="23">
         <f>C7</f>
         <v/>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>P&amp;L per 100 vol points</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="35" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Theta / year</t>
         </is>
       </c>
-      <c r="C8" s="64">
+      <c r="C8" s="23">
         <f>-Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))*Assumptions!$E$10/(2*SQRT(Assumptions!$E$7))-Assumptions!$E$8*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$6)+Assumptions!$E$9*Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$5)</f>
         <v/>
       </c>
-      <c r="D8" s="64">
+      <c r="D8" s="23">
         <f>-Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))*Assumptions!$E$10/(2*SQRT(Assumptions!$E$7))+Assumptions!$E$8*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(-'European Pricer'!$C$6)-Assumptions!$E$9*Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST(-'European Pricer'!$C$5)</f>
         <v/>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>annual time decay</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="36">
-      <c r="B9" s="35" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Rho</t>
         </is>
       </c>
-      <c r="C9" s="64">
+      <c r="C9" s="23">
         <f>Assumptions!$E$7*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$6)</f>
         <v/>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="23">
         <f>-Assumptions!$E$7*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(-'European Pricer'!$C$6)</f>
         <v/>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>rate exposure</t>
         </is>
@@ -4304,151 +4202,153 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="35" min="1" max="1"/>
-    <col width="22" customWidth="1" style="35" min="2" max="2"/>
-    <col width="13" customWidth="1" style="35" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Illustrative Volatility Surface</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="36">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Maturity / Strike</t>
         </is>
       </c>
-      <c r="C4" s="49" t="n">
+      <c r="C4" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="D4" s="49" t="n">
+      <c r="D4" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="E4" s="49" t="n">
+      <c r="E4" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="49" t="n">
+      <c r="F4" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="G4" s="49" t="n">
+      <c r="G4" s="8" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="36">
-      <c r="B5" s="65" t="n">
+    <row r="5">
+      <c r="B5" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="F5" s="63">
+      <c r="F5" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="G5" s="63">
+      <c r="G5" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="36">
-      <c r="B6" s="65" t="n">
+    <row r="6">
+      <c r="B6" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="F6" s="63">
+      <c r="F6" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="G6" s="63">
+      <c r="G6" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="36">
-      <c r="B7" s="65" t="n">
+    <row r="7">
+      <c r="B7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="36">
-      <c r="B8" s="65" t="n">
+    <row r="8">
+      <c r="B8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="F8" s="63">
+      <c r="F8" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v/>
       </c>
-      <c r="G8" s="63">
+      <c r="G8" s="22">
         <f>MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v/>
       </c>
@@ -4458,19 +4358,17 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:G8">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFE2F0D9"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFFCE4D6"/>
+        <cfvo type="max"/>
+        <color rgb="00E2F0D9"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00FCE4D6"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>